--- a/artfynd/A 24589-2022 artfynd.xlsx
+++ b/artfynd/A 24589-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24589-2022 artfynd.xlsx
+++ b/artfynd/A 24589-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125769004</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58275</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103051</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenfink</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carpodacus erythrinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kohage, Rosfors bruk nat. res., Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>799001</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7287709</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lena Bondestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lena Bondestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24589-2022 artfynd.xlsx
+++ b/artfynd/A 24589-2022 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125769004</v>
       </c>
       <c r="B3" t="n">
-        <v>58275</v>
+        <v>58276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24589-2022 artfynd.xlsx
+++ b/artfynd/A 24589-2022 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125769004</v>
       </c>
       <c r="B3" t="n">
-        <v>58276</v>
+        <v>58277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24589-2022 artfynd.xlsx
+++ b/artfynd/A 24589-2022 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125769004</v>
       </c>
       <c r="B3" t="n">
-        <v>58277</v>
+        <v>58281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24589-2022 artfynd.xlsx
+++ b/artfynd/A 24589-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,117 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133903918</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rosfors, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>798875</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7287815</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24589-2022 artfynd.xlsx
+++ b/artfynd/A 24589-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94166195</v>
+        <v>133903918</v>
       </c>
       <c r="B2" t="n">
-        <v>57000</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103051</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,31 +708,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rosfors, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798921.880008179</v>
+        <v>798875</v>
       </c>
       <c r="R2" t="n">
-        <v>7287787.330826046</v>
+        <v>7287815</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125769004</v>
+        <v>58988969</v>
       </c>
       <c r="B3" t="n">
-        <v>58281</v>
+        <v>57364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103051</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,20 +826,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kohage, Rosfors bruk nat. res., Nb</t>
+          <t>Rosfors, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>799001</v>
+        <v>798944</v>
       </c>
       <c r="R3" t="n">
-        <v>7287709</v>
+        <v>7287738</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lena Bondestad</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lena Bondestad</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133903918</v>
+        <v>94166195</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>58586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103051</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,29 +927,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rosfors, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798875</v>
+        <v>798921</v>
       </c>
       <c r="R4" t="n">
-        <v>7287815</v>
+        <v>7287787</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,12 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1004,125 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125769004</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58586</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103051</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenfink</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carpodacus erythrinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kohage, Rosfors bruk nat. res., Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>799001</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7287709</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lena Bondestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lena Bondestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24589-2022 artfynd.xlsx
+++ b/artfynd/A 24589-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133903918</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58988969</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94166195</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,8 +1143,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125769004</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>